--- a/Training Plan_Containerization using Docker and Kubernetes_52 Hours.xlsx
+++ b/Training Plan_Containerization using Docker and Kubernetes_52 Hours.xlsx
@@ -1309,7 +1309,7 @@
       <c r="D10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="13" t="s">
         <v>29</v>
       </c>
       <c r="F10" s="14"/>

--- a/Training Plan_Containerization using Docker and Kubernetes_52 Hours.xlsx
+++ b/Training Plan_Containerization using Docker and Kubernetes_52 Hours.xlsx
@@ -941,7 +941,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1022,12 +1022,16 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1327,7 +1331,7 @@
       <c r="D11" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="13" t="s">
         <v>32</v>
       </c>
       <c r="F11" s="14"/>
@@ -1381,7 +1385,7 @@
       <c r="D14" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="22" t="s">
         <v>41</v>
       </c>
       <c r="F14" s="18"/>
@@ -1399,7 +1403,7 @@
       <c r="D15" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="22" t="s">
         <v>44</v>
       </c>
       <c r="F15" s="18"/>
@@ -1456,25 +1460,25 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="3" style="3" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" s="23" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="22" t="s">
+    <row r="1" s="24" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="22"/>
-    </row>
-    <row r="2" s="23" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="24" t="s">
+      <c r="B1" s="23"/>
+    </row>
+    <row r="2" s="24" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="25" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="3" s="15" customFormat="true" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="27" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1482,7 +1486,7 @@
       <c r="A4" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="27" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1490,15 +1494,15 @@
       <c r="A5" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="27" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27"/>
+      <c r="A6" s="28"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28"/>
+      <c r="A8" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
